--- a/Result/profitability/4416.xlsx
+++ b/Result/profitability/4416.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.01125</v>
+        <v>0.47375</v>
       </c>
       <c r="N2" t="n">
-        <v>60.67625</v>
+        <v>61.20125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02125</v>
+        <v>0.445</v>
       </c>
       <c r="N3" t="n">
-        <v>56.5725</v>
+        <v>61.77124999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04625000000000001</v>
+        <v>0.65125</v>
       </c>
       <c r="N4" t="n">
-        <v>57.33125</v>
+        <v>58.1825</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3675</v>
+        <v>0.6525</v>
       </c>
       <c r="N5" t="n">
-        <v>53.515</v>
+        <v>56.44625000000001</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1030,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.37</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2525</v>
+        <v>0.8837499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>51.57375</v>
+        <v>32.08</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.96</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5575</v>
+        <v>0.90125</v>
       </c>
       <c r="N7" t="n">
-        <v>27.2025</v>
+        <v>31.24625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>0.86</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5625</v>
+        <v>0.98</v>
       </c>
       <c r="N8" t="n">
-        <v>26.45</v>
+        <v>28.37875</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.9</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8462500000000001</v>
+        <v>0.8462499999999999</v>
       </c>
       <c r="N11" t="n">
         <v>23.50875</v>
@@ -1899,7 +1899,7 @@
         <v>0.72</v>
       </c>
       <c r="M12" t="n">
-        <v>0.88875</v>
+        <v>0.8887499999999999</v>
       </c>
       <c r="N12" t="n">
         <v>23.21625</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4416</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1460</v>
+      </c>
+      <c r="D75" t="n">
+        <v>565</v>
+      </c>
+      <c r="E75" t="n">
+        <v>895</v>
+      </c>
+      <c r="F75" t="n">
+        <v>61.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>827</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>56.64%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-575</v>
+      </c>
+      <c r="J75" t="n">
+        <v>252</v>
+      </c>
+      <c r="K75" t="n">
+        <v>260</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>65.325</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X75" t="n">
+        <v>14.52173913043478</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3363121185701832</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.767441860465116</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6193872160591654</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
